--- a/public/discipline-assesment/discipline-assesment (1).xlsx
+++ b/public/discipline-assesment/discipline-assesment (1).xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cut Putri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDD7DA3-0FD1-4E67-B517-B728A5AD47D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2013A178-E2CC-4957-9E19-47AA31CC9EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10800" windowHeight="12900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>Bulan</t>
   </si>
@@ -48,29 +57,22 @@
     <t>Terlambat</t>
   </si>
   <si>
-    <t>KJ-6-134</t>
+    <t>00006</t>
   </si>
   <si>
-    <t xml:space="preserve">Rayhan Alfa Rezel </t>
+    <t>Aden Sukma Mulia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -87,19 +89,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,14 +114,8 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -148,144 +138,35 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -664,14 +545,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="7" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" customWidth="1"/>
+    <col min="5" max="7" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.1" customHeight="1">
+    <row r="1" spans="1:7" ht="23" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,101 +575,143 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75">
+    <row r="2" spans="1:7">
       <c r="A2" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4">
         <v>2025</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4">
         <v>2025</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75">
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4">
         <v>2025</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4"/>
@@ -917,27 +840,6 @@
       <c r="G21" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
